--- a/testdata/configurationTST/configuration_environment.xlsx
+++ b/testdata/configurationTST/configuration_environment.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12495" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="Conn" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -69,6 +82,9 @@
     <t>Environment</t>
   </si>
   <si>
+    <t>Platform</t>
+  </si>
+  <si>
     <t>Active</t>
   </si>
   <si>
@@ -120,9 +136,24 @@
     <t>serverLogFolder</t>
   </si>
   <si>
+    <t>dbEngineReport</t>
+  </si>
+  <si>
+    <t>dbConnectionStringReport</t>
+  </si>
+  <si>
+    <t>testRun</t>
+  </si>
+  <si>
+    <t>nameOfTestRun</t>
+  </si>
+  <si>
     <t>dev</t>
   </si>
   <si>
+    <t>Android</t>
+  </si>
+  <si>
     <t>off</t>
   </si>
   <si>
@@ -141,10 +172,7 @@
     <t>.</t>
   </si>
   <si>
-    <t>co.infinum.nlb.qa.playstore</t>
-  </si>
-  <si>
-    <t>co.infinum.nlb.qa.playstore:id/</t>
+    <t>si.nlb.klik.test</t>
   </si>
   <si>
     <t>C:\Users\Bozidar Tomasevic\AppData\Local\Programs\Appium\resources\app\node_modules\appium\build\lib\main.js</t>
@@ -168,19 +196,25 @@
     <t>jdbc:sqlserver://10.1.133.30;Database=iBankingRaiffeisenV4;User Id=sa;Password=Cerkasov123;integratedSecurity=false;</t>
   </si>
   <si>
-    <t>co.infinum.nlb.tst.playstore</t>
-  </si>
-  <si>
-    <t>co.infinum.nlb.tst.playstore:id/</t>
-  </si>
-  <si>
     <t>ON</t>
   </si>
   <si>
     <t>\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT</t>
   </si>
   <si>
-    <t>co.infinum.nlb.uat</t>
+    <t>MYSQL</t>
+  </si>
+  <si>
+    <t>jdbc:mysql://172.20.1.100:3306/dbnlbreport?user=adm1n&amp;password=Beograd123!&amp;useSSL=false</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>UAT 06 07 2023 09:36:41</t>
+  </si>
+  <si>
+    <t>si.nlb.klik.uat</t>
   </si>
   <si>
     <t>co.infinum.nlb.uat:id/</t>
@@ -205,9 +239,6 @@
   </si>
   <si>
     <t>jdbc:postgresql://localhost/test?user=postgres&amp;password=W1llkomm.n&amp;ssl=false</t>
-  </si>
-  <si>
-    <t>MYSQL</t>
   </si>
   <si>
     <t>jdbc:mysql://localhost/test?user=root&amp;password=simple</t>
@@ -216,12 +247,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -272,33 +303,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="Helvetica Neue"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="Helvetica Neue"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Helvetica Neue"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,24 +326,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Helvetica Neue"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,10 +342,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
       <name val="Helvetica Neue"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -355,16 +365,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Helvetica Neue"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Helvetica Neue"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -372,7 +375,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="Helvetica Neue"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -393,18 +396,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Helvetica Neue"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Helvetica Neue"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -435,181 +466,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,13 +845,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -836,15 +889,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -890,172 +934,159 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1065,22 +1096,22 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="7">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1122,52 +1153,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Currency" xfId="5" builtinId="4"/>
-    <cellStyle name="Percent" xfId="6" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
-    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
-    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
-    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
-    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
-    <cellStyle name="Note" xfId="12" builtinId="10"/>
-    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="Title" xfId="16" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
-    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
-    <cellStyle name="Input" xfId="21" builtinId="20"/>
-    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
-    <cellStyle name="Good" xfId="23" builtinId="26"/>
-    <cellStyle name="Output" xfId="24" builtinId="21"/>
-    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bad" xfId="29" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
-    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
-    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
-    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -2292,9 +2323,9 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="4" width="30.5047619047619" style="1" customWidth="1"/>
-    <col min="5" max="256" width="10" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="4" width="30.5092592592593" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="256" width="10" style="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:5">
@@ -2416,24 +2447,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.352380952381" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1" customWidth="1"/>
-    <col min="5" max="5" width="88.847619047619" style="1" customWidth="1"/>
-    <col min="6" max="6" width="34.1714285714286" style="1" customWidth="1"/>
-    <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5047619047619" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.5047619047619" style="1" customWidth="1"/>
-    <col min="12" max="17" width="73.352380952381" style="1" customWidth="1"/>
-    <col min="18" max="256" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3518518518519" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="6" width="88.8518518518518" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.1759259259259" style="1" customWidth="1"/>
+    <col min="8" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5092592592593" style="1" customWidth="1"/>
+    <col min="11" max="11" width="42" style="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5092592592593" style="1" customWidth="1"/>
+    <col min="13" max="18" width="73.3518518518518" style="1" customWidth="1"/>
+    <col min="19" max="257" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" spans="1:19">
+    <row r="1" ht="13.5" customHeight="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -2458,22 +2489,22 @@
       <c r="H1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="7" t="s">
         <v>22</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2485,112 +2516,145 @@
       <c r="Q1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" ht="13.5" customHeight="1" spans="1:17">
-      <c r="A2" s="5">
+      <c r="T1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" ht="13.5" customHeight="1" spans="1:24">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1" spans="1:24">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="7" t="s">
+      <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="10" t="s">
+      <c r="F3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="11"/>
-      <c r="P2" s="10" t="s">
+      <c r="I3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="J3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" ht="13.5" customHeight="1" spans="1:19">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" ht="13.5" customHeight="1" spans="1:17">
+      <c r="L3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" spans="1:24">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -2600,20 +2664,21 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-    </row>
-    <row r="5" ht="13.5" customHeight="1" spans="1:17">
+      <c r="J4" s="4"/>
+      <c r="K4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+    </row>
+    <row r="5" ht="13.5" customHeight="1" spans="1:24">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2624,15 +2689,15 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1" spans="1:17">
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" ht="13.5" customHeight="1" spans="1:24">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2650,8 +2715,9 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
-    </row>
-    <row r="7" ht="13.5" customHeight="1" spans="1:17">
+      <c r="R6" s="4"/>
+    </row>
+    <row r="7" ht="13.5" customHeight="1" spans="1:24">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2669,8 +2735,9 @@
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1" spans="1:17">
+      <c r="R7" s="4"/>
+    </row>
+    <row r="8" ht="13.5" customHeight="1" spans="1:24">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -2688,8 +2755,9 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1" spans="1:17">
+      <c r="R8" s="4"/>
+    </row>
+    <row r="9" ht="13.5" customHeight="1" spans="1:24">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2707,8 +2775,9 @@
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1" spans="1:17">
+      <c r="R9" s="4"/>
+    </row>
+    <row r="10" ht="13.5" customHeight="1" spans="1:24">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2726,10 +2795,11 @@
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="S3" r:id="rId1" display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
+    <hyperlink ref="T3" r:id="rId1" display="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT" tooltip="\\10.11.1.158\03. TEST Team\NLB SLO\FileShare\UAT"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
@@ -2743,39 +2813,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.82857142857143" defaultRowHeight="14.45" customHeight="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.82407407407407" defaultRowHeight="14.45" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.6761904761905" style="1" customWidth="1"/>
-    <col min="2" max="2" width="68.352380952381" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5047619047619" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6761904761905" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.67619047619048" style="1" customWidth="1"/>
-    <col min="6" max="256" width="8.84761904761905" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6759259259259" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="68.3518518518518" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="7.50925925925926" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="11.6759259259259" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="9.67592592592593" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="256" width="8.85185185185185" style="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.5" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -2783,27 +2853,27 @@
     </row>
     <row r="3" ht="13.5" customHeight="1" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2811,10 +2881,10 @@
     </row>
     <row r="5" ht="13.5" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
